--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15100000</v>
+        <v>16821.93</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9600000</v>
+        <v>10694.74</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1465000</v>
+        <v>1632.06</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7700000</v>
+        <v>8578.07</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9469759</v>
+        <v>10549.64</v>
       </c>
     </row>
     <row r="7">
@@ -870,17 +870,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>20339565</v>
+        <v>22658.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2328-434-CM26</t>
+          <t>2292-6483-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,53 +895,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>En Proceso</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t xml:space="preserve">RENTUR CHILE SPA </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.241.697-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>18320000</v>
+        <v>17499.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2292-6483-CM26</t>
+          <t>2428-425-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,53 +956,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTUR CHILE SPA </t>
+          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.241.697-2</t>
+          <t>15.751.336-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>15708000</v>
+        <v>22536.93</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2428-425-CM26</t>
+          <t>2674-396-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,48 +1022,48 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.751.336-2</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>20230000</v>
+        <v>6439.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2674-396-CM26</t>
+          <t>5522-38-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,28 +1103,28 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>MARCELO FABIAN</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5780000</v>
+        <v>7798.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5522-38-CM26</t>
+          <t>2467-466-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,43 +1149,43 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7000000</v>
+        <v>7174.39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2467-466-CM26</t>
+          <t>1375758-42-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,48 +1205,48 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6440000</v>
+        <v>5637.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1375758-42-CM26</t>
+          <t>5522-39-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,28 +1286,28 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>MARCELO FABIAN</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5060000</v>
+        <v>1782.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5522-39-CM26</t>
+          <t>1030177-70-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,43 +1332,43 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>JULIÁN LEONARDO HIDALGO QUILODRÁN</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>10.992.223-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1600000</v>
+        <v>66743.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1030177-70-CM26</t>
+          <t>4454-395-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.150.600-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1419,17 +1419,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>59911740</v>
+        <v>13179.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4454-395-CM26</t>
+          <t>997-52-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,53 +1444,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.150.600-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>JULIÁN LEONARDO HIDALGO QUILODRÁN</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10.992.223-4</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11830000</v>
+        <v>61271.78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>997-52-CM26</t>
+          <t>4404-54-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,53 +1505,53 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>MARPACIFICO SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>77.173.533-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>54999872</v>
+        <v>55673.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4404-54-CM26</t>
+          <t>2307-603-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,43 +1576,43 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t>RENT A CAR SUR LTDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
+          <t>76.683.282-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>49975000</v>
+        <v>12526.21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2307-603-CM26</t>
+          <t>4766-3491-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,43 +1637,43 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>RENT A CAR SUR LTDA</t>
+          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.683.282-2</t>
+          <t>76.345.484-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>11244000</v>
+        <v>6628.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4766-3491-CM26</t>
+          <t>5744-18-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,53 +1688,53 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.345.484-3</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5950000</v>
+        <v>1806.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5744-18-CM26</t>
+          <t>2467-533-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,53 +1749,53 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1621851</v>
+        <v>623.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2467-533-CM26</t>
+          <t>750-42-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,48 +1815,48 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>LUCANO RENT A CAR S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.813.177-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>560000</v>
+        <v>2508.81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>750-42-CM26</t>
+          <t>3517-70-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,42 +1876,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LUCANO RENT A CAR S.A.</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.813.177-5</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2252004</v>
+        <v>8912.280000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1968,17 +1968,17 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>20360000</v>
+        <v>22681.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3517-70-CM26</t>
+          <t>1176-39-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,43 +2003,43 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8000000</v>
+        <v>23862.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1176-39-CM26</t>
+          <t>162-194-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,53 +2054,53 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>Vivanet</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.018.259-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>21420000</v>
+        <v>40831.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>162-194-CM26</t>
+          <t>511077-46-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,43 +2125,43 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>36652000</v>
+        <v>4344.74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>511077-46-CM26</t>
+          <t>2102-387-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,43 +2186,43 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Transportes Myriam y Sergio Ltda.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.343.454-0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3900000</v>
+        <v>38501.05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2102-387-CM26</t>
+          <t>2102-388-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2273,17 +2273,17 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>34560000</v>
+        <v>38501.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2102-388-CM26</t>
+          <t>2467-534-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,48 +2303,48 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Transportes Myriam y Sergio Ltda.</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.343.454-0</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>34560000</v>
+        <v>10382.81</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2467-534-CM26</t>
+          <t>1375758-45-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,53 +2359,53 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9320000</v>
+        <v>8321.84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1375758-45-CM26</t>
+          <t>1121-47-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,22 +2445,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7470000</v>
+        <v>75.42</v>
       </c>
     </row>
     <row r="34">
@@ -2517,17 +2517,17 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>38663520</v>
+        <v>43072.51</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>930-85-CM26</t>
+          <t>615-25-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,43 +2552,43 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.802.006-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>ALEJANDRO BRAULIO PARRA TAMAYO</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>10.521.479-0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1560000</v>
+        <v>10026.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1121-47-CM26</t>
+          <t>930-85-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,43 +2613,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>67699</v>
+        <v>1737.89</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>615-25-CM26</t>
+          <t>2291-880-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,43 +2674,43 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.802.006-1</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ALEJANDRO BRAULIO PARRA TAMAYO</t>
+          <t xml:space="preserve">RENTUR CHILE SPA </t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>10.521.479-0</t>
+          <t>76.241.697-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>9000000</v>
+        <v>23171.93</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2291-880-CM26</t>
+          <t>299-85-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2730,48 +2730,48 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTUR CHILE SPA </t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.241.697-2</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>20800000</v>
+        <v>52860.96</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>299-85-CM26</t>
+          <t>3334-228-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,28 +2811,28 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>SOCIEDAD AUTOMOTRIZ MACKENNA LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.013.794-4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>47450000</v>
+        <v>15219.05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3334-228-CM26</t>
+          <t>1134432-403-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,48 +2852,48 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOCIEDAD AUTOMOTRIZ MACKENNA LIMITADA</t>
+          <t xml:space="preserve">FELIPE </t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.013.794-4</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>13661200</v>
+        <v>1667.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1134432-403-CM26</t>
+          <t>5522-47-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,53 +2908,53 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1496900</v>
+        <v>2932.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5522-47-CM26</t>
+          <t>568658-846-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,48 +2974,48 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2632416</v>
+        <v>26736.84</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>568658-846-CM26</t>
+          <t>3446-118-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,28 +3055,28 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>AUTOMOTRIZ R y R LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>24000000</v>
+        <v>10750.44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3446-118-CM26</t>
+          <t>1434-94-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3096,103 +3096,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección General de Aeronáutica Civil</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>9650000</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>1434-94-CM26</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2239-12-LR25</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>61.104.022-9</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Dirección General de Aeronáutica Civil</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>SMC</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>76.310.505-9</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>360000000</v>
+        <v>401052.58</v>
       </c>
     </row>
   </sheetData>
